--- a/exports/BANDHANBNK_full_report.xlsx
+++ b/exports/BANDHANBNK_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q79"/>
+  <dimension ref="A1:U79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,25 +557,25 @@
         <v>8</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44613.55208333334</v>
+        <v>44614.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>313.25</v>
+        <v>303.65</v>
       </c>
       <c r="I2" t="n">
         <v>305.3004915458677</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>43</v>
       </c>
       <c r="K2" t="n">
-        <v>14.81</v>
+        <v>11.29</v>
       </c>
       <c r="L2" t="n">
         <v>1.76</v>
       </c>
       <c r="M2" t="n">
-        <v>2.36</v>
+        <v>2.63</v>
       </c>
       <c r="N2" t="n">
         <v>2.36</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>8.039999999999999</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44634.55208333334</v>
+        <v>44635.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>267.3</v>
+        <v>282.7</v>
       </c>
       <c r="I3" t="n">
         <v>282.5811880465525</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K3" t="n">
-        <v>11.97</v>
+        <v>6.9</v>
       </c>
       <c r="L3" t="n">
         <v>4.64</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>12.07</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44691.38541666666</v>
+        <v>44691.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>315.35</v>
+        <v>312.6</v>
       </c>
       <c r="I4" t="n">
         <v>313.2575209723954</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>56</v>
+        <v>56.16666666666666</v>
       </c>
       <c r="K4" t="n">
-        <v>11.55</v>
+        <v>10.58</v>
       </c>
       <c r="L4" t="n">
         <v>4.63</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>8.529999999999999</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44694.55208333334</v>
+        <v>44697.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>318</v>
+        <v>336.95</v>
       </c>
       <c r="I5" t="n">
         <v>331.6469519420614</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>3</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.73</v>
+        <v>-7.79</v>
       </c>
       <c r="L5" t="n">
-        <v>6.33</v>
+        <v>9.66</v>
       </c>
       <c r="M5" t="n">
-        <v>1.06</v>
+        <v>1.95</v>
       </c>
       <c r="N5" t="n">
-        <v>3.99</v>
+        <v>6.6</v>
       </c>
       <c r="O5" t="n">
         <v>-0.38</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>13.75</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44722.55208333334</v>
+        <v>44725.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>323.4</v>
+        <v>306.35</v>
       </c>
       <c r="I6" t="n">
         <v>313.275769109066</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K6" t="n">
-        <v>-4.02</v>
+        <v>-9.08</v>
       </c>
       <c r="L6" t="n">
         <v>10.37</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>9.31</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44761.38541666666</v>
+        <v>44761.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>282.05</v>
+        <v>287.8</v>
       </c>
       <c r="I7" t="n">
         <v>286.9811871203618</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>36</v>
+        <v>36.16666666666666</v>
       </c>
       <c r="K7" t="n">
-        <v>7.93</v>
+        <v>6.06</v>
       </c>
       <c r="L7" t="n">
         <v>5.89</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,25 +971,25 @@
         <v>7.54</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44799.55208333334</v>
+        <v>44802.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>286.3</v>
+        <v>275.05</v>
       </c>
       <c r="I8" t="n">
         <v>280.7804299038399</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>38</v>
+        <v>40.83333333333334</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.52</v>
+        <v>-4.43</v>
       </c>
       <c r="L8" t="n">
         <v>7.52</v>
       </c>
       <c r="M8" t="n">
-        <v>0.52</v>
+        <v>2.27</v>
       </c>
       <c r="N8" t="n">
         <v>4.36</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>8.35</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44817.38541666666</v>
+        <v>44817.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>289.85</v>
+        <v>297.9</v>
       </c>
       <c r="I9" t="n">
         <v>293.8506903701192</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K9" t="n">
-        <v>-5.38</v>
+        <v>-8.31</v>
       </c>
       <c r="L9" t="n">
-        <v>8.050000000000001</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="M9" t="n">
         <v>1.09</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>7.02</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44823.38541666666</v>
+        <v>44823.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>291.85</v>
+        <v>289.25</v>
       </c>
       <c r="I10" t="n">
         <v>289.7197074242118</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>5.833333333333333</v>
+        <v>6</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.03</v>
+        <v>-2.9</v>
       </c>
       <c r="L10" t="n">
         <v>3.66</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>7.54</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44838.55208333334</v>
+        <v>44840.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>270.8</v>
+        <v>275.25</v>
       </c>
       <c r="I11" t="n">
         <v>275.2263290005105</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>15</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K11" t="n">
-        <v>6.38</v>
+        <v>4.84</v>
       </c>
       <c r="L11" t="n">
         <v>2.85</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>7.79</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44862.55208333334</v>
+        <v>44865.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>265.2</v>
+        <v>241.3</v>
       </c>
       <c r="I12" t="n">
         <v>259.8361694130567</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.65</v>
+        <v>-12.33</v>
       </c>
       <c r="L12" t="n">
-        <v>5.34</v>
+        <v>13.64</v>
       </c>
       <c r="M12" t="n">
         <v>2.06</v>
       </c>
       <c r="N12" t="n">
-        <v>2.57</v>
+        <v>9.73</v>
       </c>
       <c r="O12" t="n">
         <v>1.14</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>12.61</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44890.55208333334</v>
+        <v>44893.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>219.2</v>
+        <v>224.5</v>
       </c>
       <c r="I13" t="n">
         <v>223.4259318039175</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K13" t="n">
-        <v>9.16</v>
+        <v>6.96</v>
       </c>
       <c r="L13" t="n">
         <v>7.75</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>6.34</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44916.55208333334</v>
+        <v>44917.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>242.95</v>
+        <v>230.6</v>
       </c>
       <c r="I14" t="n">
         <v>239.8158799247226</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K14" t="n">
-        <v>8.220000000000001</v>
+        <v>2.72</v>
       </c>
       <c r="L14" t="n">
         <v>2.34</v>
@@ -1239,7 +1406,7 @@
         <v>0.24</v>
       </c>
       <c r="N14" t="n">
-        <v>1.73</v>
+        <v>4.84</v>
       </c>
       <c r="O14" t="n">
         <v>1.94</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>11.13</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44932.55208333334</v>
+        <v>44935.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>243.2</v>
+        <v>246.7</v>
       </c>
       <c r="I15" t="n">
         <v>246.1309860726594</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K15" t="n">
-        <v>-5.46</v>
+        <v>-6.98</v>
       </c>
       <c r="L15" t="n">
         <v>8.15</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>9.67</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44958.55208333334</v>
+        <v>44959.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>237</v>
+        <v>226.2</v>
       </c>
       <c r="I16" t="n">
         <v>234.3220202835202</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K16" t="n">
-        <v>-3.93</v>
+        <v>-8.31</v>
       </c>
       <c r="L16" t="n">
-        <v>6.67</v>
+        <v>8.98</v>
       </c>
       <c r="M16" t="n">
-        <v>0.21</v>
+        <v>0.63</v>
       </c>
       <c r="N16" t="n">
-        <v>1.86</v>
+        <v>3.63</v>
       </c>
       <c r="O16" t="n">
         <v>1.4</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>12.02</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45019.38541666666</v>
+        <v>45019.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>203.85</v>
+        <v>204.75</v>
       </c>
       <c r="I17" t="n">
         <v>203.9424954376342</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>60</v>
+        <v>60.16666666666666</v>
       </c>
       <c r="K17" t="n">
-        <v>9.880000000000001</v>
+        <v>9.48</v>
       </c>
       <c r="L17" t="n">
         <v>8.31</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>8.960000000000001</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45090.55208333334</v>
+        <v>45091.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>261.05</v>
+        <v>253.05</v>
       </c>
       <c r="I18" t="n">
         <v>255.9088262362633</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>71</v>
+        <v>71.83333333333333</v>
       </c>
       <c r="K18" t="n">
-        <v>27.5</v>
+        <v>23.59</v>
       </c>
       <c r="L18" t="n">
         <v>1.34</v>
@@ -1467,7 +1682,7 @@
         <v>1.7</v>
       </c>
       <c r="N18" t="n">
-        <v>2.52</v>
+        <v>3.2</v>
       </c>
       <c r="O18" t="n">
         <v>4.6</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>7.22</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45135.55208333334</v>
+        <v>45138.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>217.05</v>
+        <v>224.15</v>
       </c>
       <c r="I19" t="n">
         <v>222.7082219496924</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>44.16666666666666</v>
+        <v>47</v>
       </c>
       <c r="K19" t="n">
-        <v>14.23</v>
+        <v>11.42</v>
       </c>
       <c r="L19" t="n">
         <v>3.54</v>
@@ -1524,7 +1751,7 @@
         <v>1.53</v>
       </c>
       <c r="N19" t="n">
-        <v>2.97</v>
+        <v>3.25</v>
       </c>
       <c r="O19" t="n">
         <v>-3.2</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>6.86</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45181.38541666666</v>
+        <v>45181.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>233.35</v>
+        <v>232</v>
       </c>
       <c r="I20" t="n">
         <v>232.9118408013533</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>43</v>
+        <v>43.16666666666666</v>
       </c>
       <c r="K20" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="L20" t="n">
         <v>3.06</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>6.02</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45183.55208333334</v>
+        <v>45184.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>240</v>
+        <v>245.85</v>
       </c>
       <c r="I21" t="n">
         <v>245.3971173752089</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>2</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.45</v>
+        <v>-5.97</v>
       </c>
       <c r="L21" t="n">
-        <v>4.07</v>
+        <v>6.68</v>
       </c>
       <c r="M21" t="n">
         <v>0.8</v>
       </c>
       <c r="N21" t="n">
-        <v>1.77</v>
+        <v>3.62</v>
       </c>
       <c r="O21" t="n">
         <v>-4.53</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>6.95</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45212.38541666666</v>
+        <v>45212.55208333334</v>
       </c>
       <c r="H22" t="n">
-        <v>245.1</v>
+        <v>239.25</v>
       </c>
       <c r="I22" t="n">
         <v>241.4757096075631</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>28</v>
+        <v>28.16666666666667</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.31</v>
+        <v>-2.68</v>
       </c>
       <c r="L22" t="n">
-        <v>2.73</v>
+        <v>3.19</v>
       </c>
       <c r="M22" t="n">
         <v>1.5</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>7.24</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45258.55208333334</v>
+        <v>45259.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>217.25</v>
+        <v>222.55</v>
       </c>
       <c r="I23" t="n">
         <v>219.1394248379525</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>46</v>
+        <v>46.83333333333334</v>
       </c>
       <c r="K23" t="n">
-        <v>9.199999999999999</v>
+        <v>6.98</v>
       </c>
       <c r="L23" t="n">
         <v>2.82</v>
@@ -1752,7 +2027,7 @@
         <v>1.15</v>
       </c>
       <c r="N23" t="n">
-        <v>2.38</v>
+        <v>2.51</v>
       </c>
       <c r="O23" t="n">
         <v>-4.49</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>5.16</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45280.38541666666</v>
+        <v>45280.55208333334</v>
       </c>
       <c r="H24" t="n">
-        <v>245.05</v>
+        <v>238.5</v>
       </c>
       <c r="I24" t="n">
         <v>240.6045459529656</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K24" t="n">
-        <v>10.11</v>
+        <v>7.17</v>
       </c>
       <c r="L24" t="n">
         <v>2.61</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>7.76</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45293.55208333334</v>
+        <v>45294.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>241.9</v>
+        <v>257.25</v>
       </c>
       <c r="I25" t="n">
         <v>249.3658635388987</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.43</v>
+        <v>-7.86</v>
       </c>
       <c r="L25" t="n">
-        <v>3.56</v>
+        <v>8.24</v>
       </c>
       <c r="M25" t="n">
         <v>1.2</v>
       </c>
       <c r="N25" t="n">
-        <v>1.04</v>
+        <v>4.86</v>
       </c>
       <c r="O25" t="n">
         <v>-4.14</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>9.34</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45296.55208333334</v>
+        <v>45299.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>252</v>
+        <v>235.9</v>
       </c>
       <c r="I26" t="n">
         <v>243.3364498914109</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.04</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>6.32</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="M26" t="n">
         <v>0.02</v>
       </c>
       <c r="N26" t="n">
-        <v>3.36</v>
+        <v>7.76</v>
       </c>
       <c r="O26" t="n">
         <v>4.86</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>12.42</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45383.55208333334</v>
+        <v>45384.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>188</v>
+        <v>192.2</v>
       </c>
       <c r="I27" t="n">
         <v>189.1068577252444</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>84.16666666666667</v>
+        <v>85</v>
       </c>
       <c r="K27" t="n">
-        <v>20.31</v>
+        <v>18.52</v>
       </c>
       <c r="L27" t="n">
         <v>6.82</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>113</v>
+        <v>114</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>4</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>6.47</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45387.55208333334</v>
+        <v>45390.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>197.6</v>
+        <v>185.9</v>
       </c>
       <c r="I28" t="n">
         <v>188.2216711968824</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K28" t="n">
-        <v>2.81</v>
+        <v>-3.28</v>
       </c>
       <c r="L28" t="n">
-        <v>2.37</v>
+        <v>6.74</v>
       </c>
       <c r="M28" t="n">
-        <v>0.52</v>
+        <v>6.33</v>
       </c>
       <c r="N28" t="n">
-        <v>1.09</v>
+        <v>6.33</v>
       </c>
       <c r="O28" t="n">
         <v>2.66</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>7.51</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45404.55208333334</v>
+        <v>45405.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>181.05</v>
+        <v>182.25</v>
       </c>
       <c r="I29" t="n">
         <v>182.0308582107658</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K29" t="n">
-        <v>2.61</v>
+        <v>1.96</v>
       </c>
       <c r="L29" t="n">
         <v>1.8</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>5.62</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45418.55208333334</v>
+        <v>45419.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>186.55</v>
+        <v>180.7</v>
       </c>
       <c r="I30" t="n">
         <v>181.3136527959238</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K30" t="n">
-        <v>2.36</v>
+        <v>-0.85</v>
       </c>
       <c r="L30" t="n">
-        <v>0.63</v>
+        <v>0.85</v>
       </c>
       <c r="M30" t="n">
         <v>0.05</v>
       </c>
       <c r="N30" t="n">
-        <v>1.57</v>
+        <v>2.81</v>
       </c>
       <c r="O30" t="n">
         <v>0.88</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>7.74</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45440.55208333334</v>
+        <v>45441.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>189.3</v>
+        <v>191.5</v>
       </c>
       <c r="I31" t="n">
         <v>190.9128596230745</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K31" t="n">
-        <v>-4.76</v>
+        <v>-5.98</v>
       </c>
       <c r="L31" t="n">
-        <v>7</v>
+        <v>7.42</v>
       </c>
       <c r="M31" t="n">
         <v>0.8100000000000001</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>5.91</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>194.8</v>
+        <v>179.2</v>
       </c>
       <c r="I32" t="n">
         <v>183.4751245796844</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K32" t="n">
-        <v>1.72</v>
+        <v>-6.42</v>
       </c>
       <c r="L32" t="n">
-        <v>3.37</v>
+        <v>11.67</v>
       </c>
       <c r="M32" t="n">
-        <v>0.37</v>
+        <v>0.41</v>
       </c>
       <c r="N32" t="n">
-        <v>2.43</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="O32" t="n">
         <v>1.22</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>11.16</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45449.55208333334</v>
+        <v>45450.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>191.45</v>
+        <v>197.15</v>
       </c>
       <c r="I33" t="n">
         <v>196.9356490904556</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K33" t="n">
-        <v>-6.84</v>
+        <v>-10.02</v>
       </c>
       <c r="L33" t="n">
-        <v>8.710000000000001</v>
+        <v>10.38</v>
       </c>
       <c r="M33" t="n">
         <v>0.79</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>10.22</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45482.55208333334</v>
+        <v>45483.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>200.45</v>
+        <v>193.18</v>
       </c>
       <c r="I34" t="n">
         <v>198.2758840288651</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>33</v>
       </c>
       <c r="K34" t="n">
-        <v>1.67</v>
+        <v>-2.01</v>
       </c>
       <c r="L34" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="M34" t="n">
         <v>3.61</v>
       </c>
       <c r="N34" t="n">
-        <v>1.91</v>
+        <v>4.02</v>
       </c>
       <c r="O34" t="n">
         <v>2.27</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>8.52</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45499.55208333334</v>
+        <v>45502.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>192.6</v>
+        <v>216.76</v>
       </c>
       <c r="I35" t="n">
         <v>199.9427590257324</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K35" t="n">
-        <v>0.3</v>
+        <v>-12.21</v>
       </c>
       <c r="L35" t="n">
-        <v>5.06</v>
+        <v>12.95</v>
       </c>
       <c r="M35" t="n">
-        <v>0.75</v>
+        <v>5.4</v>
       </c>
       <c r="N35" t="n">
-        <v>3.72</v>
+        <v>13.44</v>
       </c>
       <c r="O35" t="n">
         <v>-4.02</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>12.83</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45509.38541666666</v>
+        <v>45509.55208333334</v>
       </c>
       <c r="H36" t="n">
-        <v>202.71</v>
+        <v>201.65</v>
       </c>
       <c r="I36" t="n">
         <v>201.6634939606058</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K36" t="n">
-        <v>-6.48</v>
+        <v>-6.97</v>
       </c>
       <c r="L36" t="n">
         <v>7.68</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>8.220000000000001</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45524.55208333334</v>
+        <v>45525.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>196.9</v>
+        <v>202.13</v>
       </c>
       <c r="I37" t="n">
         <v>201.8451997096343</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>15</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="K37" t="n">
-        <v>2.36</v>
+        <v>-0.24</v>
       </c>
       <c r="L37" t="n">
         <v>2.41</v>
@@ -2550,7 +2993,7 @@
         <v>1.66</v>
       </c>
       <c r="N37" t="n">
-        <v>2.31</v>
+        <v>3.48</v>
       </c>
       <c r="O37" t="n">
         <v>-5.11</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>6.4</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45532.38541666666</v>
+        <v>45532.55208333334</v>
       </c>
       <c r="H38" t="n">
-        <v>198.21</v>
+        <v>196.29</v>
       </c>
       <c r="I38" t="n">
         <v>196.3615904955608</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K38" t="n">
-        <v>-1.94</v>
+        <v>-2.89</v>
       </c>
       <c r="L38" t="n">
-        <v>2.54</v>
+        <v>2.97</v>
       </c>
       <c r="M38" t="n">
         <v>0.02</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>5.42</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45537.55208333334</v>
+        <v>45538.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>201.39</v>
+        <v>203.7</v>
       </c>
       <c r="I39" t="n">
         <v>203.2425495369802</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>5</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K39" t="n">
-        <v>-2.6</v>
+        <v>-3.78</v>
       </c>
       <c r="L39" t="n">
-        <v>3.74</v>
+        <v>4.23</v>
       </c>
       <c r="M39" t="n">
         <v>0.57</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>5.72</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45562.55208333334</v>
+        <v>45565.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>203.93</v>
+        <v>199.18</v>
       </c>
       <c r="I40" t="n">
         <v>200.8993254278841</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K40" t="n">
-        <v>0.11</v>
+        <v>-2.22</v>
       </c>
       <c r="L40" t="n">
         <v>4.93</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>6.93</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45575.55208333334</v>
+        <v>45576.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>187.9</v>
+        <v>205.82</v>
       </c>
       <c r="I41" t="n">
         <v>196.1598896483265</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K41" t="n">
-        <v>5.66</v>
+        <v>-3.33</v>
       </c>
       <c r="L41" t="n">
-        <v>2.61</v>
+        <v>5.18</v>
       </c>
       <c r="M41" t="n">
-        <v>1.61</v>
+        <v>7.5</v>
       </c>
       <c r="N41" t="n">
-        <v>2.44</v>
+        <v>11.39</v>
       </c>
       <c r="O41" t="n">
         <v>-2.69</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>8.460000000000001</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45581.55208333334</v>
+        <v>45582.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>192.99</v>
+        <v>189.34</v>
       </c>
       <c r="I42" t="n">
         <v>192.786303866077</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K42" t="n">
-        <v>-6.23</v>
+        <v>-8.01</v>
       </c>
       <c r="L42" t="n">
-        <v>6.78</v>
+        <v>8.48</v>
       </c>
       <c r="M42" t="n">
         <v>0.2</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>8.119999999999999</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45590.55208333334</v>
+        <v>45593.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>169.1</v>
+        <v>183.93</v>
       </c>
       <c r="I43" t="n">
         <v>183.6750393053231</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K43" t="n">
-        <v>10.69</v>
+        <v>2.86</v>
       </c>
       <c r="L43" t="n">
         <v>2.17</v>
       </c>
       <c r="M43" t="n">
-        <v>0.03</v>
+        <v>3.49</v>
       </c>
       <c r="N43" t="n">
-        <v>4.45</v>
+        <v>9.02</v>
       </c>
       <c r="O43" t="n">
         <v>-1.31</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>12.74</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45608.55208333334</v>
+        <v>45609.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>172.01</v>
+        <v>166.26</v>
       </c>
       <c r="I44" t="n">
         <v>171.8123888744526</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K44" t="n">
-        <v>-6.48</v>
+        <v>-9.609999999999999</v>
       </c>
       <c r="L44" t="n">
-        <v>6.49</v>
+        <v>9.99</v>
       </c>
       <c r="M44" t="n">
         <v>1.22</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>8.119999999999999</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45629.55208333334</v>
+        <v>45630.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>175.07</v>
+        <v>178.1</v>
       </c>
       <c r="I45" t="n">
         <v>175.8304703943556</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K45" t="n">
-        <v>-5.3</v>
+        <v>-7.12</v>
       </c>
       <c r="L45" t="n">
-        <v>5.86</v>
+        <v>7.21</v>
       </c>
       <c r="M45" t="n">
         <v>2.56</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,25 +3593,25 @@
         <v>5.49</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45638.55208333334</v>
+        <v>45639.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>170.55</v>
+        <v>168.23</v>
       </c>
       <c r="I46" t="n">
         <v>170.1454497318097</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K46" t="n">
-        <v>-4.24</v>
+        <v>-5.54</v>
       </c>
       <c r="L46" t="n">
-        <v>4.54</v>
+        <v>7.01</v>
       </c>
       <c r="M46" t="n">
-        <v>0.2</v>
+        <v>0.32</v>
       </c>
       <c r="N46" t="n">
         <v>2.17</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>4.61</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45671.38541666666</v>
+        <v>45671.55208333334</v>
       </c>
       <c r="H47" t="n">
-        <v>144.65</v>
+        <v>149.05</v>
       </c>
       <c r="I47" t="n">
         <v>148.0798502554634</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>32</v>
+        <v>32.16666666666666</v>
       </c>
       <c r="K47" t="n">
-        <v>14.02</v>
+        <v>11.4</v>
       </c>
       <c r="L47" t="n">
         <v>1.65</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>8.85</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45698.55208333334</v>
+        <v>45699.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>148.8</v>
+        <v>144</v>
       </c>
       <c r="I48" t="n">
         <v>144.1911797691909</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>27</v>
+        <v>27.83333333333333</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.17</v>
+        <v>-3.39</v>
       </c>
       <c r="L48" t="n">
-        <v>3.22</v>
+        <v>3.51</v>
       </c>
       <c r="M48" t="n">
         <v>2.08</v>
       </c>
       <c r="N48" t="n">
-        <v>2.31</v>
+        <v>3.09</v>
       </c>
       <c r="O48" t="n">
         <v>8.199999999999999</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,25 +3800,25 @@
         <v>8.43</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45708.55208333334</v>
+        <v>45709.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>136.33</v>
+        <v>140.49</v>
       </c>
       <c r="I49" t="n">
         <v>139.4487175352762</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K49" t="n">
-        <v>5.33</v>
+        <v>2.44</v>
       </c>
       <c r="L49" t="n">
         <v>3.4</v>
       </c>
       <c r="M49" t="n">
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="N49" t="n">
         <v>2.69</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>8.050000000000001</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45726.55208333334</v>
+        <v>45727.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>147.5</v>
+        <v>139.06</v>
       </c>
       <c r="I50" t="n">
         <v>140.5512771678553</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K50" t="n">
-        <v>4.99</v>
+        <v>-1.02</v>
       </c>
       <c r="L50" t="n">
         <v>4.58</v>
       </c>
       <c r="M50" t="n">
-        <v>1.17</v>
+        <v>1.83</v>
       </c>
       <c r="N50" t="n">
-        <v>2.81</v>
+        <v>4.66</v>
       </c>
       <c r="O50" t="n">
         <v>1.89</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>10.45</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45741.55208333334</v>
+        <v>45742.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>147.32</v>
+        <v>150</v>
       </c>
       <c r="I51" t="n">
         <v>148.60318457602</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K51" t="n">
-        <v>-5.94</v>
+        <v>-7.87</v>
       </c>
       <c r="L51" t="n">
-        <v>8.41</v>
+        <v>9.66</v>
       </c>
       <c r="M51" t="n">
         <v>2.13</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>6.12</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>153.41</v>
+        <v>143.29</v>
       </c>
       <c r="I52" t="n">
         <v>145.5069656786549</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K52" t="n">
-        <v>2.27</v>
+        <v>-4.47</v>
       </c>
       <c r="L52" t="n">
-        <v>3.6</v>
+        <v>5.67</v>
       </c>
       <c r="M52" t="n">
-        <v>0.99</v>
+        <v>5.48</v>
       </c>
       <c r="N52" t="n">
-        <v>2.13</v>
+        <v>4.93</v>
       </c>
       <c r="O52" t="n">
         <v>0.78</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>9.57</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45762.55208333334</v>
+        <v>45763.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>154.01</v>
+        <v>158.07</v>
       </c>
       <c r="I53" t="n">
         <v>156.9061883182345</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K53" t="n">
-        <v>-7.48</v>
+        <v>-10.31</v>
       </c>
       <c r="L53" t="n">
-        <v>7.85</v>
+        <v>10.58</v>
       </c>
       <c r="M53" t="n">
         <v>2.39</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>8.34</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45782.55208333334</v>
+        <v>45783.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>164.4</v>
+        <v>158.75</v>
       </c>
       <c r="I54" t="n">
         <v>160.8328014532215</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K54" t="n">
-        <v>4</v>
+        <v>0.43</v>
       </c>
       <c r="L54" t="n">
         <v>2.53</v>
@@ -3519,7 +4166,7 @@
         <v>0.4</v>
       </c>
       <c r="N54" t="n">
-        <v>2.79</v>
+        <v>4.33</v>
       </c>
       <c r="O54" t="n">
         <v>2.81</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>10.34</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45790.55208333334</v>
+        <v>45791.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>162.7</v>
+        <v>167.68</v>
       </c>
       <c r="I55" t="n">
         <v>167.6563607210043</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K55" t="n">
-        <v>-2.49</v>
+        <v>-5.63</v>
       </c>
       <c r="L55" t="n">
-        <v>4.57</v>
+        <v>5.7</v>
       </c>
       <c r="M55" t="n">
         <v>3.19</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>8.710000000000001</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45841.55208333334</v>
+        <v>45842.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>183.5</v>
+        <v>178.45</v>
       </c>
       <c r="I56" t="n">
         <v>180.7874575986942</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>50.16666666666666</v>
+        <v>51</v>
       </c>
       <c r="K56" t="n">
-        <v>9.43</v>
+        <v>6.42</v>
       </c>
       <c r="L56" t="n">
         <v>3.54</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>6.26</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45853.55208333334</v>
+        <v>45854.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>179.97</v>
+        <v>183.48</v>
       </c>
       <c r="I57" t="n">
         <v>182.7477131719333</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.85</v>
+        <v>-2.82</v>
       </c>
       <c r="L57" t="n">
-        <v>2.24</v>
+        <v>3</v>
       </c>
       <c r="M57" t="n">
         <v>0.13</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>5.94</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45863.55208333334</v>
+        <v>45866.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>178.24</v>
+        <v>176.02</v>
       </c>
       <c r="I58" t="n">
         <v>177.4345522855976</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K58" t="n">
-        <v>-2.86</v>
+        <v>-4.07</v>
       </c>
       <c r="L58" t="n">
-        <v>3.7</v>
+        <v>4.12</v>
       </c>
       <c r="M58" t="n">
         <v>2.43</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>5.87</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45887.55208333334</v>
+        <v>45888.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>167.45</v>
+        <v>172.91</v>
       </c>
       <c r="I59" t="n">
         <v>170.251042542434</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K59" t="n">
-        <v>4.87</v>
+        <v>1.77</v>
       </c>
       <c r="L59" t="n">
         <v>1.68</v>
@@ -3804,7 +4511,7 @@
         <v>1.03</v>
       </c>
       <c r="N59" t="n">
-        <v>3.02</v>
+        <v>3.91</v>
       </c>
       <c r="O59" t="n">
         <v>-1.54</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>7.34</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45894.55208333334</v>
+        <v>45895.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>171.35</v>
+        <v>166.14</v>
       </c>
       <c r="I60" t="n">
         <v>168.9639787847171</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.9</v>
+        <v>-3.92</v>
       </c>
       <c r="L60" t="n">
         <v>4.26</v>
@@ -3861,7 +4580,7 @@
         <v>0.51</v>
       </c>
       <c r="N60" t="n">
-        <v>1.76</v>
+        <v>3.43</v>
       </c>
       <c r="O60" t="n">
         <v>3.91</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>6.61</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45931.38541666666</v>
+        <v>45931.55208333334</v>
       </c>
       <c r="H61" t="n">
-        <v>162.48</v>
+        <v>163.38</v>
       </c>
       <c r="I61" t="n">
         <v>162.9158183930317</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>36</v>
+        <v>36.16666666666666</v>
       </c>
       <c r="K61" t="n">
-        <v>2.2</v>
+        <v>1.66</v>
       </c>
       <c r="L61" t="n">
         <v>3.19</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>5.2</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45960.55208333334</v>
+        <v>45961.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>169.64</v>
+        <v>157.86</v>
       </c>
       <c r="I62" t="n">
         <v>166.6882316704338</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>29</v>
+        <v>29.83333333333333</v>
       </c>
       <c r="K62" t="n">
-        <v>3.83</v>
+        <v>-3.38</v>
       </c>
       <c r="L62" t="n">
-        <v>2.43</v>
+        <v>3.52</v>
       </c>
       <c r="M62" t="n">
-        <v>0.3</v>
+        <v>3.27</v>
       </c>
       <c r="N62" t="n">
-        <v>3.1</v>
+        <v>7.74</v>
       </c>
       <c r="O62" t="n">
         <v>0.67</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>9.300000000000001</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46002.38541666666</v>
+        <v>46002.55208333334</v>
       </c>
       <c r="H63" t="n">
-        <v>143.07</v>
+        <v>145</v>
       </c>
       <c r="I63" t="n">
         <v>144.7004491556099</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>41</v>
+        <v>41.16666666666666</v>
       </c>
       <c r="K63" t="n">
-        <v>9.369999999999999</v>
+        <v>8.15</v>
       </c>
       <c r="L63" t="n">
         <v>4.46</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>6.39</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46034.55208333334</v>
+        <v>46035.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>143.86</v>
+        <v>141.31</v>
       </c>
       <c r="I64" t="n">
         <v>142.9898144134005</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>32</v>
+        <v>32.83333333333334</v>
       </c>
       <c r="K64" t="n">
-        <v>-0.79</v>
+        <v>-2.54</v>
       </c>
       <c r="L64" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="M64" t="n">
         <v>0.83</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>6.36</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46044.55208333334</v>
+        <v>46045.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>143</v>
+        <v>151.54</v>
       </c>
       <c r="I65" t="n">
         <v>146.1242259854564</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K65" t="n">
-        <v>-1.2</v>
+        <v>-7.24</v>
       </c>
       <c r="L65" t="n">
-        <v>3.32</v>
+        <v>7.67</v>
       </c>
       <c r="M65" t="n">
-        <v>0.76</v>
+        <v>5.03</v>
       </c>
       <c r="N65" t="n">
-        <v>3.66</v>
+        <v>3.92</v>
       </c>
       <c r="O65" t="n">
         <v>-0.3</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>8.77</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46087.55208333334</v>
+        <v>46090.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>183</v>
+        <v>173.92</v>
       </c>
       <c r="I66" t="n">
         <v>174.8697231525195</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>45</v>
       </c>
       <c r="K66" t="n">
-        <v>20.76</v>
+        <v>14.77</v>
       </c>
       <c r="L66" t="n">
         <v>4.25</v>
       </c>
       <c r="M66" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="N66" t="n">
-        <v>4.14</v>
+        <v>4.54</v>
       </c>
       <c r="O66" t="n">
         <v>3.92</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>3</v>
+      </c>
+      <c r="U66" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>9.25</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>149.22</v>
+        <v>161.39</v>
       </c>
       <c r="I67" t="n">
         <v>155.6588286153604</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K67" t="n">
-        <v>14.2</v>
+        <v>7.2</v>
       </c>
       <c r="L67" t="n">
         <v>6.26</v>
       </c>
       <c r="M67" t="n">
-        <v>2.47</v>
+        <v>4.01</v>
       </c>
       <c r="N67" t="n">
-        <v>4.7</v>
+        <v>10.54</v>
       </c>
       <c r="O67" t="n">
         <v>-4.54</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>11.66</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46157.55208333334</v>
+        <v>46160.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>194.1</v>
+        <v>189.87</v>
       </c>
       <c r="I68" t="n">
         <v>192.9283779896491</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>37.16666666666666</v>
+        <v>40</v>
       </c>
       <c r="K68" t="n">
-        <v>20.27</v>
+        <v>17.65</v>
       </c>
       <c r="L68" t="n">
         <v>3.84</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,28 +5180,28 @@
         <v>7.52</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46168.55208333334</v>
+        <v>46169.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>201.25</v>
+        <v>207.24</v>
       </c>
       <c r="I69" t="n">
         <v>202.0696609368287</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K69" t="n">
-        <v>-5.99</v>
+        <v>-9.15</v>
       </c>
       <c r="L69" t="n">
-        <v>7.28</v>
+        <v>9.69</v>
       </c>
       <c r="M69" t="n">
         <v>1.03</v>
       </c>
       <c r="N69" t="n">
-        <v>1.83</v>
+        <v>2.36</v>
       </c>
       <c r="O69" t="n">
         <v>-1.9</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,22 +5249,22 @@
         <v>7.68</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46183.55208333334</v>
+        <v>46184.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>200.59</v>
+        <v>195.02</v>
       </c>
       <c r="I70" t="n">
         <v>196.120440281663</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K70" t="n">
-        <v>-3.21</v>
+        <v>-5.9</v>
       </c>
       <c r="L70" t="n">
-        <v>4.05</v>
+        <v>5.91</v>
       </c>
       <c r="M70" t="n">
         <v>1.42</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4467,22 +5318,22 @@
         <v>9</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46185.55208333334</v>
+        <v>46188.38541666666</v>
       </c>
       <c r="H71" t="n">
-        <v>205.98</v>
+        <v>212.81</v>
       </c>
       <c r="I71" t="n">
         <v>207.6148529598685</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K71" t="n">
-        <v>-5.62</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="L71" t="n">
-        <v>5.72</v>
+        <v>10.21</v>
       </c>
       <c r="M71" t="n">
         <v>2.01</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S71" t="b">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>1</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>8.289999999999999</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46206.38541666666</v>
+        <v>46206.55208333334</v>
       </c>
       <c r="H72" t="n">
-        <v>200.7</v>
+        <v>199.46</v>
       </c>
       <c r="I72" t="n">
         <v>200.2632438235592</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>18</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="K72" t="n">
-        <v>-5.69</v>
+        <v>-6.27</v>
       </c>
       <c r="L72" t="n">
         <v>7.19</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,22 +5456,22 @@
         <v>6.64</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46216.38541666666</v>
+        <v>46216.55208333334</v>
       </c>
       <c r="H73" t="n">
-        <v>210</v>
+        <v>212.53</v>
       </c>
       <c r="I73" t="n">
         <v>212.5183080409658</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>9.833333333333334</v>
+        <v>10</v>
       </c>
       <c r="K73" t="n">
-        <v>-5.28</v>
+        <v>-6.55</v>
       </c>
       <c r="L73" t="n">
-        <v>6.74</v>
+        <v>7.39</v>
       </c>
       <c r="M73" t="n">
         <v>0.6</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S73" t="b">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>1</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -4638,28 +5525,28 @@
         <v>7.12</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46224.55208333334</v>
+        <v>46225.38541666666</v>
       </c>
       <c r="H74" t="n">
-        <v>207.5</v>
+        <v>174.9</v>
       </c>
       <c r="I74" t="n">
         <v>201.3092879046349</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K74" t="n">
-        <v>-2.37</v>
+        <v>-17.71</v>
       </c>
       <c r="L74" t="n">
-        <v>2.88</v>
+        <v>20.22</v>
       </c>
       <c r="M74" t="n">
-        <v>2.13</v>
+        <v>9.42</v>
       </c>
       <c r="N74" t="n">
-        <v>2.18</v>
+        <v>16.05</v>
       </c>
       <c r="O74" t="n">
         <v>1.45</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S74" t="b">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4695,19 +5594,19 @@
         <v>16.95</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46272.55208333334</v>
+        <v>46273.38541666666</v>
       </c>
       <c r="H75" t="n">
-        <v>164.05</v>
+        <v>168.53</v>
       </c>
       <c r="I75" t="n">
         <v>168.2962942108341</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>47.16666666666666</v>
+        <v>48</v>
       </c>
       <c r="K75" t="n">
-        <v>6.2</v>
+        <v>3.64</v>
       </c>
       <c r="L75" t="n">
         <v>9.9</v>
@@ -4716,7 +5615,7 @@
         <v>1.23</v>
       </c>
       <c r="N75" t="n">
-        <v>2.77</v>
+        <v>4.61</v>
       </c>
       <c r="O75" t="n">
         <v>-16.05</v>
@@ -4725,7 +5624,19 @@
         <v>1</v>
       </c>
       <c r="Q75" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>3</v>
+      </c>
+      <c r="U75" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="76">
@@ -4752,19 +5663,19 @@
         <v>6.46</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46294.55208333334</v>
+        <v>46295.38541666666</v>
       </c>
       <c r="H76" t="n">
-        <v>182.25</v>
+        <v>179.47</v>
       </c>
       <c r="I76" t="n">
         <v>179.6748519910125</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K76" t="n">
-        <v>8.140000000000001</v>
+        <v>6.49</v>
       </c>
       <c r="L76" t="n">
         <v>3.1</v>
@@ -4782,7 +5693,19 @@
         <v>1</v>
       </c>
       <c r="Q76" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>2</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -4809,28 +5732,28 @@
         <v>8.19</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46307.55208333334</v>
+        <v>46308.38541666666</v>
       </c>
       <c r="H77" t="n">
-        <v>157.01</v>
+        <v>169.23</v>
       </c>
       <c r="I77" t="n">
         <v>168.9663018030235</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K77" t="n">
-        <v>12.51</v>
+        <v>5.71</v>
       </c>
       <c r="L77" t="n">
         <v>2.73</v>
       </c>
       <c r="M77" t="n">
-        <v>0.97</v>
+        <v>3.18</v>
       </c>
       <c r="N77" t="n">
-        <v>1.08</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="O77" t="n">
         <v>-2.33</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S77" t="b">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>1</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -4866,28 +5801,28 @@
         <v>10.74</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46317.55208333334</v>
+        <v>46318.38541666666</v>
       </c>
       <c r="H78" t="n">
-        <v>158.55</v>
+        <v>149.8</v>
       </c>
       <c r="I78" t="n">
         <v>156.6791433830444</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K78" t="n">
-        <v>-6.31</v>
+        <v>-11.48</v>
       </c>
       <c r="L78" t="n">
-        <v>7.7</v>
+        <v>11.79</v>
       </c>
       <c r="M78" t="n">
         <v>1</v>
       </c>
       <c r="N78" t="n">
-        <v>2.75</v>
+        <v>5.4</v>
       </c>
       <c r="O78" t="n">
         <v>9.550000000000001</v>
@@ -4896,7 +5831,19 @@
         <v>1</v>
       </c>
       <c r="Q78" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S78" t="b">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>1</v>
+      </c>
+      <c r="U78" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -4947,6 +5894,12 @@
       <c r="Q79" t="n">
         <v>6</v>
       </c>
+      <c r="R79" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7049,7 +8002,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.5</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="6">
@@ -7059,7 +8012,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16.2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
@@ -7069,7 +8022,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>84.2</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8">
@@ -7079,7 +8032,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="9">
@@ -7089,7 +8042,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29.2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10">
@@ -7099,7 +8052,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>43.5</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="11">
@@ -7139,7 +8092,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.62</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="15">
@@ -7149,7 +8102,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.42</v>
+        <v>-1.42</v>
       </c>
     </row>
     <row r="16">
@@ -7159,7 +8112,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.83</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="17">
@@ -7169,7 +8122,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>27.5</v>
+        <v>23.59</v>
       </c>
     </row>
     <row r="18">
@@ -7179,7 +8132,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>51.9</v>
+        <v>37.7</v>
       </c>
     </row>
     <row r="19">
@@ -7189,7 +8142,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.62</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="20">
@@ -7199,7 +8152,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.05</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="21">
@@ -7209,7 +8162,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10.37</v>
+        <v>20.22</v>
       </c>
     </row>
     <row r="22">
@@ -7219,7 +8172,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23">
@@ -7229,7 +8182,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
@@ -7239,7 +8192,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.38</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="25">
@@ -7249,7 +8202,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3.92</v>
+        <v>9.42</v>
       </c>
     </row>
     <row r="26">
@@ -7259,7 +8212,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.3</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="27">
@@ -7269,7 +8222,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>8.199999999999999</v>
+        <v>16.05</v>
       </c>
     </row>
     <row r="28">
@@ -7279,7 +8232,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29">
